--- a/Result/profitability/8096.xlsx
+++ b/Result/profitability/8096.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.62375</v>
+        <v>0.5737499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7375</v>
+        <v>3.79</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4212499999999999</v>
+        <v>0.55375</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>3.98625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4037499999999999</v>
+        <v>0.4437499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>4.22375</v>
+        <v>3.91625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3074999999999999</v>
+        <v>0.5462499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2875</v>
+        <v>4.29125</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4037499999999999</v>
+        <v>0.57875</v>
       </c>
       <c r="N6" t="n">
-        <v>4.77625</v>
+        <v>4.83375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>-0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39875</v>
+        <v>0.5349999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2275</v>
+        <v>5.100000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.76</v>
       </c>
       <c r="M8" t="n">
-        <v>0.455</v>
+        <v>0.3925</v>
       </c>
       <c r="N8" t="n">
-        <v>5.537500000000001</v>
+        <v>5.0725</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9832,6 +9832,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8096</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>17317</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16895</v>
+      </c>
+      <c r="E75" t="n">
+        <v>422</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G75" t="n">
+        <v>172</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>166</v>
+      </c>
+      <c r="K75" t="n">
+        <v>209</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2631578947368421</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.72</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.6038961038961039</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.745098039215686</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.0299999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01244813278008294</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
